--- a/Course List/Course list.xlsx
+++ b/Course List/Course list.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cynth\Desktop\StatsDiscordBot\Course List\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DBF965-9D65-47E9-9A82-FEFD7547FE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891D1088-A18E-4628-B9B7-6DF180B6CC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14595" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="14483" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NCUFN" sheetId="1" r:id="rId1"/>
     <sheet name="NCUEC" sheetId="2" r:id="rId2"/>
     <sheet name="CYCUIUBM" sheetId="3" r:id="rId3"/>
-    <sheet name="CYCUBA" sheetId="6" r:id="rId4"/>
-    <sheet name="HWIS" sheetId="4" r:id="rId5"/>
+    <sheet name="CYCUBA" sheetId="4" r:id="rId4"/>
+    <sheet name="HWIS" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="356">
   <si>
     <t>StudentID</t>
   </si>
@@ -35,37 +35,1063 @@
     <t>Password</t>
   </si>
   <si>
+    <t>侯昕宜</t>
+  </si>
+  <si>
+    <t>丁聖曦</t>
+  </si>
+  <si>
+    <t>CYCUIUBM</t>
+  </si>
+  <si>
+    <t>盧安琪</t>
+  </si>
+  <si>
+    <t>溫堅強</t>
+  </si>
+  <si>
+    <t>阮重勝</t>
+  </si>
+  <si>
+    <t>陳德</t>
+  </si>
+  <si>
+    <t>password: davent2705</t>
+  </si>
+  <si>
+    <t>陳勳</t>
+  </si>
+  <si>
+    <t>Pass:02052003</t>
+  </si>
+  <si>
+    <t>劉雯惠</t>
+  </si>
+  <si>
+    <t>陳義範</t>
+  </si>
+  <si>
+    <t>Intac2026!</t>
+  </si>
+  <si>
+    <t>馮明凱</t>
+  </si>
+  <si>
+    <t>intac2026</t>
+  </si>
+  <si>
+    <t>葉明煜</t>
+  </si>
+  <si>
+    <t>password: alv1t0</t>
+  </si>
+  <si>
+    <t>周榮仙</t>
+  </si>
+  <si>
+    <t>林麗燕</t>
+  </si>
+  <si>
+    <t>lalalostu17</t>
+  </si>
+  <si>
+    <t>邱文琪</t>
+  </si>
+  <si>
+    <t>萬兆霖</t>
+  </si>
+  <si>
+    <t>StatisticBil</t>
+  </si>
+  <si>
+    <t>裴銘鈞</t>
+  </si>
+  <si>
+    <t>@Minhquan2006</t>
+  </si>
+  <si>
+    <t>呂寶安</t>
+  </si>
+  <si>
+    <t>高須陽菜</t>
+  </si>
+  <si>
+    <t>hina0320</t>
+  </si>
+  <si>
+    <t>姚美貞</t>
+  </si>
+  <si>
+    <t>Supercali123</t>
+  </si>
+  <si>
+    <t>周海玲</t>
+  </si>
+  <si>
+    <t>範英玉</t>
+  </si>
+  <si>
+    <t>Jadepham1906</t>
+  </si>
+  <si>
+    <t>李喬安</t>
+  </si>
+  <si>
+    <t>Statistics.5555</t>
+  </si>
+  <si>
+    <t>周遵平</t>
+  </si>
+  <si>
+    <t>tSOSB9607!!</t>
+  </si>
+  <si>
+    <t>徐家旺</t>
+  </si>
+  <si>
+    <t>蔡恩典</t>
+  </si>
+  <si>
+    <t>吉海朝陽</t>
+  </si>
+  <si>
+    <t>張恩榮</t>
+  </si>
+  <si>
+    <t>Stevenyes25</t>
+  </si>
+  <si>
+    <t>翁秀之</t>
+  </si>
+  <si>
+    <t>prot123</t>
+  </si>
+  <si>
+    <t>賈凱文</t>
+  </si>
+  <si>
+    <t>Calvin231808</t>
+  </si>
+  <si>
+    <t>方佳麗</t>
+  </si>
+  <si>
+    <t>ECherylA</t>
+  </si>
+  <si>
+    <t>劉心愛</t>
+  </si>
+  <si>
+    <t>L144sta8</t>
+  </si>
+  <si>
+    <t>黄奕翔</t>
+  </si>
+  <si>
+    <t>Mar2176_</t>
+  </si>
+  <si>
+    <t>吳輝天</t>
+  </si>
+  <si>
+    <t>KotiJelek</t>
+  </si>
+  <si>
+    <t>侯植生</t>
+  </si>
+  <si>
+    <t>Teti0921</t>
+  </si>
+  <si>
+    <t>鄭立志</t>
+  </si>
+  <si>
     <t>葉錦徽</t>
   </si>
   <si>
+    <t>NCUFN</t>
+  </si>
+  <si>
+    <t>徐珮淇</t>
+  </si>
+  <si>
+    <t>1214</t>
+  </si>
+  <si>
+    <t>池翊寧</t>
+  </si>
+  <si>
+    <t>pipja0-zujriw-pincUf</t>
+  </si>
+  <si>
+    <t>鄭雨辰</t>
+  </si>
+  <si>
+    <t>Tel202066</t>
+  </si>
+  <si>
+    <t>謝秉炘</t>
+  </si>
+  <si>
+    <t>盧多珈</t>
+  </si>
+  <si>
+    <t>ncufn112707502</t>
+  </si>
+  <si>
+    <t>賴品宜</t>
+  </si>
+  <si>
+    <t>113101501</t>
+  </si>
+  <si>
+    <t>曾子綺</t>
+  </si>
+  <si>
+    <t>may0531</t>
+  </si>
+  <si>
+    <t>李亦桓</t>
+  </si>
+  <si>
+    <t>ncu369963ncu</t>
+  </si>
+  <si>
+    <t>賴小雨</t>
+  </si>
+  <si>
+    <t>詹旭家</t>
+  </si>
+  <si>
+    <t>statistic#113409026</t>
+  </si>
+  <si>
+    <t>黃宣寧</t>
+  </si>
+  <si>
+    <t>林奕璇</t>
+  </si>
+  <si>
+    <t>ayiM0603</t>
+  </si>
+  <si>
+    <t>黃郁惟</t>
+  </si>
+  <si>
+    <t>114408002</t>
+  </si>
+  <si>
+    <t>陳宥熙</t>
+  </si>
+  <si>
+    <t>1510</t>
+  </si>
+  <si>
+    <t>陳寶妮</t>
+  </si>
+  <si>
+    <t>mhjh2007</t>
+  </si>
+  <si>
+    <t>林佳儀</t>
+  </si>
+  <si>
+    <t>Stella0112.</t>
+  </si>
+  <si>
+    <t>游曼琳</t>
+  </si>
+  <si>
+    <t>bta5306</t>
+  </si>
+  <si>
+    <t>顏芝琪</t>
+  </si>
+  <si>
+    <t>1211</t>
+  </si>
+  <si>
+    <t>吳卉榆</t>
+  </si>
+  <si>
+    <t>Why85600719!</t>
+  </si>
+  <si>
+    <t>林妤芸</t>
+  </si>
+  <si>
+    <t>lin2007</t>
+  </si>
+  <si>
+    <t>簡詣臻</t>
+  </si>
+  <si>
+    <t>pibo0825</t>
+  </si>
+  <si>
+    <t>宋詠忻</t>
+  </si>
+  <si>
+    <t>fay510216</t>
+  </si>
+  <si>
+    <t>鍾秋香</t>
+  </si>
+  <si>
+    <t>NcuLogin4827</t>
+  </si>
+  <si>
+    <t>黃慧玲</t>
+  </si>
+  <si>
+    <t>huilingstats07</t>
+  </si>
+  <si>
+    <t>劉弈宏</t>
+  </si>
+  <si>
+    <t>GdxTy70708181</t>
+  </si>
+  <si>
+    <t>陳立恆</t>
+  </si>
+  <si>
+    <t>12345678</t>
+  </si>
+  <si>
+    <t>葉秉洋</t>
+  </si>
+  <si>
+    <t>960324</t>
+  </si>
+  <si>
+    <t>王柏恩</t>
+  </si>
+  <si>
+    <t>1314520</t>
+  </si>
+  <si>
+    <t>楊閎翔</t>
+  </si>
+  <si>
+    <t>郭名祥</t>
+  </si>
+  <si>
+    <t>許文謙</t>
+  </si>
+  <si>
+    <t>abcd9999</t>
+  </si>
+  <si>
+    <t>李海銓</t>
+  </si>
+  <si>
+    <t>11110807</t>
+  </si>
+  <si>
+    <t>黃品翰</t>
+  </si>
+  <si>
+    <t>何毓婕</t>
+  </si>
+  <si>
+    <t>hyj070113</t>
+  </si>
+  <si>
+    <t>陳聿盺</t>
+  </si>
+  <si>
+    <t>114408503</t>
+  </si>
+  <si>
+    <t>顏伶容</t>
+  </si>
+  <si>
+    <t>ZOE1231</t>
+  </si>
+  <si>
+    <t>吳婉寧</t>
+  </si>
+  <si>
+    <t>Ww-239201</t>
+  </si>
+  <si>
+    <t>黃家馨</t>
+  </si>
+  <si>
+    <t>Aa12345678@</t>
+  </si>
+  <si>
+    <t>楊淨涵</t>
+  </si>
+  <si>
+    <t>賴幸蓁</t>
+  </si>
+  <si>
+    <t>Lxz1111033</t>
+  </si>
+  <si>
+    <t>吳欣臻</t>
+  </si>
+  <si>
+    <t>李杺穎</t>
+  </si>
+  <si>
+    <t>114408511aaa</t>
+  </si>
+  <si>
+    <t>岩韋辰</t>
+  </si>
+  <si>
+    <t>960226</t>
+  </si>
+  <si>
+    <t>劉宥辛</t>
+  </si>
+  <si>
+    <t>陳盈穎</t>
+  </si>
+  <si>
+    <t>Finance@111394</t>
+  </si>
+  <si>
+    <t>廖苡媞</t>
+  </si>
+  <si>
+    <t>2007960819</t>
+  </si>
+  <si>
+    <t>呂妤柔</t>
+  </si>
+  <si>
+    <t>黃湘晴</t>
+  </si>
+  <si>
+    <t>洪鈺淳</t>
+  </si>
+  <si>
+    <t>Discord2468</t>
+  </si>
+  <si>
+    <t>黃詠琦</t>
+  </si>
+  <si>
+    <t>970324</t>
+  </si>
+  <si>
+    <t>王靖妤</t>
+  </si>
+  <si>
+    <t>114408520</t>
+  </si>
+  <si>
+    <t>施憶婷</t>
+  </si>
+  <si>
+    <t>Aa20070105</t>
+  </si>
+  <si>
+    <t>廖妤珊</t>
+  </si>
+  <si>
+    <t>n226812442</t>
+  </si>
+  <si>
+    <t>李秉澄</t>
+  </si>
+  <si>
+    <t>200707</t>
+  </si>
+  <si>
+    <t>唐傳宗</t>
+  </si>
+  <si>
+    <t>123asd123asdzxc</t>
+  </si>
+  <si>
+    <t>唐培恩</t>
+  </si>
+  <si>
+    <t>forever1</t>
+  </si>
+  <si>
+    <t>陳乾宥</t>
+  </si>
+  <si>
+    <t>蕭宇程</t>
+  </si>
+  <si>
+    <t>brook96222</t>
+  </si>
+  <si>
+    <t>陳宥融</t>
+  </si>
+  <si>
+    <t>48081702</t>
+  </si>
+  <si>
+    <t>莊又霖</t>
+  </si>
+  <si>
+    <t>謝瑀家</t>
+  </si>
+  <si>
+    <t>hyc0329</t>
+  </si>
+  <si>
+    <t>侯宇澤</t>
+  </si>
+  <si>
+    <t>林宇宸</t>
+  </si>
+  <si>
+    <t>20070423</t>
+  </si>
+  <si>
+    <t>李東育</t>
+  </si>
+  <si>
+    <t>Leo302023</t>
+  </si>
+  <si>
+    <t>林宸安</t>
+  </si>
+  <si>
+    <t>anxo216315</t>
+  </si>
+  <si>
+    <t>黃振軒</t>
+  </si>
+  <si>
+    <t>121RB9B133</t>
+  </si>
+  <si>
+    <t>吳銘憲</t>
+  </si>
+  <si>
+    <t>thomaswu0111</t>
+  </si>
+  <si>
+    <t>楊凱翔</t>
+  </si>
+  <si>
+    <t>陳品亦</t>
+  </si>
+  <si>
+    <t>114408539</t>
+  </si>
+  <si>
+    <t>陳國興</t>
+  </si>
+  <si>
+    <t>朱珊瑩</t>
+  </si>
+  <si>
     <t>翁祺鈞</t>
   </si>
   <si>
-    <t>朱珊瑩</t>
-  </si>
-  <si>
-    <t>NCUFN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>NCUEC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>許姵暄</t>
+  </si>
+  <si>
+    <t>bonbonoct21</t>
+  </si>
+  <si>
+    <t>蔡坤龍</t>
+  </si>
+  <si>
+    <t>andy20041225</t>
+  </si>
+  <si>
+    <t>江玉如</t>
+  </si>
+  <si>
+    <t>ruby622853</t>
+  </si>
+  <si>
+    <t>計道揆</t>
+  </si>
+  <si>
+    <t>Bommie_44</t>
+  </si>
+  <si>
+    <t>黃毓婷</t>
+  </si>
+  <si>
+    <t>黃翊茹</t>
+  </si>
+  <si>
+    <t>931117</t>
+  </si>
+  <si>
+    <t>彭芷翎</t>
+  </si>
+  <si>
+    <t>113101506</t>
+  </si>
+  <si>
+    <t>章哲駿</t>
+  </si>
+  <si>
+    <t>a41484039</t>
+  </si>
+  <si>
+    <t>林正</t>
+  </si>
+  <si>
+    <t>郭書庭</t>
+  </si>
+  <si>
+    <t>grace.777</t>
+  </si>
+  <si>
+    <t>謝佩恩</t>
+  </si>
+  <si>
+    <t>林宥希</t>
+  </si>
+  <si>
+    <t>you777</t>
+  </si>
+  <si>
+    <t>邱語薇</t>
+  </si>
+  <si>
+    <t>hww74225</t>
+  </si>
+  <si>
+    <t>江晏慈</t>
+  </si>
+  <si>
+    <t>ytch005</t>
+  </si>
+  <si>
+    <t>王清清</t>
+  </si>
+  <si>
+    <t>段生芹</t>
+  </si>
+  <si>
+    <t>李文清</t>
+  </si>
+  <si>
+    <t>陳駱洹</t>
+  </si>
+  <si>
+    <t>鄧兆棋</t>
+  </si>
+  <si>
+    <t>CDF123</t>
+  </si>
+  <si>
+    <t>林靖庾</t>
+  </si>
+  <si>
+    <t>110508</t>
+  </si>
+  <si>
+    <t>謝承諺</t>
+  </si>
+  <si>
+    <t>黃昱綸</t>
+  </si>
+  <si>
+    <t>魏宇辰</t>
+  </si>
+  <si>
+    <t>向定恩</t>
+  </si>
+  <si>
+    <t>Apple666</t>
+  </si>
+  <si>
+    <t>邵暐茹</t>
+  </si>
+  <si>
+    <t>@Asdf147</t>
+  </si>
+  <si>
+    <t>簡禾秦</t>
+  </si>
+  <si>
+    <t>jojo073</t>
+  </si>
+  <si>
+    <t>徐昱樺</t>
+  </si>
+  <si>
+    <t>echu1015</t>
+  </si>
+  <si>
+    <t>陳佳豫</t>
+  </si>
+  <si>
+    <t>mgc1479</t>
+  </si>
+  <si>
+    <t>葉思琪</t>
+  </si>
+  <si>
+    <t>xie114409507</t>
+  </si>
+  <si>
+    <t>陳柔薇</t>
+  </si>
+  <si>
+    <t>00612123</t>
+  </si>
+  <si>
+    <t>劉采瑜</t>
+  </si>
+  <si>
+    <t>50241011</t>
+  </si>
+  <si>
+    <t>李芷妤</t>
+  </si>
+  <si>
+    <t>鄭甄儀</t>
+  </si>
+  <si>
+    <t>52665</t>
+  </si>
+  <si>
+    <t>許婉婷</t>
+  </si>
+  <si>
+    <t>張惟智</t>
+  </si>
+  <si>
+    <t>weee1111</t>
+  </si>
+  <si>
+    <t>林宥亘</t>
+  </si>
+  <si>
+    <t>孟繁軒</t>
+  </si>
+  <si>
+    <t>130mke</t>
+  </si>
+  <si>
+    <t>鄭丞弼</t>
+  </si>
+  <si>
+    <t>zcbi0121</t>
+  </si>
+  <si>
+    <t>謝定軒</t>
+  </si>
+  <si>
+    <t>sam1268roger9527</t>
+  </si>
+  <si>
+    <t>楊上逸</t>
+  </si>
+  <si>
+    <t>陳世恩</t>
+  </si>
+  <si>
+    <t>135790Ba</t>
+  </si>
+  <si>
+    <t>胡廷恩</t>
+  </si>
+  <si>
+    <t>idkusewhatsoya</t>
+  </si>
+  <si>
+    <t>陳正翊</t>
+  </si>
+  <si>
+    <t>徐志瑜</t>
+  </si>
+  <si>
+    <t>陳昱宏</t>
+  </si>
+  <si>
+    <t>Cyh_1227</t>
+  </si>
+  <si>
+    <t>李奇霖</t>
+  </si>
+  <si>
+    <t>charlie123</t>
+  </si>
+  <si>
+    <t>劉慕深</t>
+  </si>
+  <si>
+    <t>楊瑞昕</t>
+  </si>
+  <si>
+    <t>qweasdzxc12345</t>
+  </si>
+  <si>
+    <t>武英舒</t>
+  </si>
+  <si>
+    <t>food1301</t>
+  </si>
+  <si>
+    <t>西村龍乃介</t>
+  </si>
+  <si>
+    <t>阮氏雪茹</t>
   </si>
   <si>
     <t>CYCUBA</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CYCUIUBM</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>侯昕宜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>丁聖曦</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>劉玉賢</t>
+  </si>
+  <si>
+    <t>陳柏儒</t>
+  </si>
+  <si>
+    <t>陳世謀</t>
+  </si>
+  <si>
+    <t>王淳立</t>
+  </si>
+  <si>
+    <t>131216945</t>
+  </si>
+  <si>
+    <t>劉昕妮</t>
+  </si>
+  <si>
+    <t>沈定緯</t>
+  </si>
+  <si>
+    <t>張家銘</t>
+  </si>
+  <si>
+    <t>kyar812</t>
+  </si>
+  <si>
+    <t>黃彥綸</t>
+  </si>
+  <si>
+    <t>陳芊曦</t>
+  </si>
+  <si>
+    <t>謝欣倪</t>
+  </si>
+  <si>
+    <t>楊舒心</t>
+  </si>
+  <si>
+    <t>詹珈寧</t>
+  </si>
+  <si>
+    <t>tmiikhswbl</t>
+  </si>
+  <si>
+    <t>陳君豪</t>
+  </si>
+  <si>
+    <t>LAG89673</t>
+  </si>
+  <si>
+    <t>羅禾展</t>
+  </si>
+  <si>
+    <t>zzzz101128</t>
+  </si>
+  <si>
+    <t>郭佩璇</t>
+  </si>
+  <si>
+    <t>周琪臻</t>
+  </si>
+  <si>
+    <t>系統密碼：Emily0524</t>
+  </si>
+  <si>
+    <t>蔡旻育</t>
+  </si>
+  <si>
+    <t>李品萱</t>
+  </si>
+  <si>
+    <t>莊晴文</t>
+  </si>
+  <si>
+    <t>簡悅綺</t>
+  </si>
+  <si>
+    <t>梁緁芯</t>
+  </si>
+  <si>
+    <t>張云婕</t>
+  </si>
+  <si>
+    <t>林禹彤</t>
+  </si>
+  <si>
+    <t>jessicalin711</t>
+  </si>
+  <si>
+    <t>胡睿育</t>
+  </si>
+  <si>
+    <t>黃奕凡</t>
+  </si>
+  <si>
+    <t>康思涵</t>
+  </si>
+  <si>
+    <t>吳紫琳</t>
+  </si>
+  <si>
+    <t>莊閔丞</t>
+  </si>
+  <si>
+    <t>林玹希</t>
+  </si>
+  <si>
+    <t>何懿紜</t>
+  </si>
+  <si>
+    <t>mnt_0314</t>
+  </si>
+  <si>
+    <t>蔡雨棠</t>
+  </si>
+  <si>
+    <t>Tt11417</t>
+  </si>
+  <si>
+    <t>褚庭萱</t>
+  </si>
+  <si>
+    <t>wdps0412</t>
+  </si>
+  <si>
+    <t>楊舒璇</t>
+  </si>
+  <si>
+    <t>林宥樺</t>
+  </si>
+  <si>
+    <t>潘竑廷</t>
+  </si>
+  <si>
+    <t>蔡宇柔</t>
+  </si>
+  <si>
+    <t>黃英慈</t>
+  </si>
+  <si>
+    <t>楊雅丞</t>
+  </si>
+  <si>
+    <t>陳子恩</t>
+  </si>
+  <si>
+    <t>郭依綾</t>
+  </si>
+  <si>
+    <t>Linda1214</t>
+  </si>
+  <si>
+    <t>范羽軒</t>
+  </si>
+  <si>
+    <t>許溱育</t>
+  </si>
+  <si>
+    <t>李立安</t>
+  </si>
+  <si>
+    <t>黃莘雅</t>
+  </si>
+  <si>
+    <t>李虹穎</t>
+  </si>
+  <si>
+    <t>楊欣樺</t>
+  </si>
+  <si>
+    <t>余翊萱</t>
+  </si>
+  <si>
+    <t>Passcode: cycu34114a</t>
+  </si>
+  <si>
+    <t>林叡弘</t>
+  </si>
+  <si>
+    <t>陳芯瑜</t>
+  </si>
+  <si>
+    <t>賴姿妤</t>
+  </si>
+  <si>
+    <t>蘇紫嫺</t>
+  </si>
+  <si>
+    <t>劉芷瑄</t>
+  </si>
+  <si>
+    <t>張廷維</t>
+  </si>
+  <si>
+    <t>劉高喬</t>
+  </si>
+  <si>
+    <t>呂美樺</t>
+  </si>
+  <si>
+    <t>Mjq021212</t>
+  </si>
+  <si>
+    <t>魏昀柔</t>
+  </si>
+  <si>
+    <t>李旻恩</t>
+  </si>
+  <si>
+    <t>鍾沁筠</t>
+  </si>
+  <si>
+    <t>李曜宇</t>
+  </si>
+  <si>
+    <t>劉晏菱</t>
+  </si>
+  <si>
+    <t>1qa2ws3ed</t>
+  </si>
+  <si>
+    <t>黃稚萱</t>
+  </si>
+  <si>
+    <t>陳姿穎</t>
+  </si>
+  <si>
+    <t>陳奐廷</t>
+  </si>
+  <si>
+    <t>陳焮如</t>
+  </si>
+  <si>
+    <t>Rrrr661414</t>
+  </si>
+  <si>
+    <t>宮木遙</t>
+  </si>
+  <si>
+    <t>Kuma1127</t>
+  </si>
+  <si>
+    <t>德永絢姫</t>
+  </si>
+  <si>
+    <t>Tokunaga3</t>
   </si>
 </sst>
 </file>
@@ -159,13 +1185,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -472,20 +1495,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.35546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -494,7 +1517,7 @@
         <v>8142122</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>8142122</v>
@@ -505,9 +1528,779 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="C3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>111302026</v>
+      </c>
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>112302534</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>112408016</v>
+      </c>
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>112408302</v>
+      </c>
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>112707502</v>
+      </c>
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>113101501</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>113101504</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>113408021</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>113409011</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>113409026</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>114401538</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>114408001</v>
+      </c>
+      <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>114408002</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>114408003</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>114408004</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>114408005</v>
+      </c>
+      <c r="B19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>114408006</v>
+      </c>
+      <c r="B20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>114408007</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>114408008</v>
+      </c>
+      <c r="B22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>114408010</v>
+      </c>
+      <c r="B23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>114408011</v>
+      </c>
+      <c r="B24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>114408012</v>
+      </c>
+      <c r="B25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>114408013</v>
+      </c>
+      <c r="B26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>114408015</v>
+      </c>
+      <c r="B27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <v>114408017</v>
+      </c>
+      <c r="B28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <v>114408019</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>114408020</v>
+      </c>
+      <c r="B30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <v>114408021</v>
+      </c>
+      <c r="B31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>114408022</v>
+      </c>
+      <c r="B32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>114408023</v>
+      </c>
+      <c r="B33" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>114408025</v>
+      </c>
+      <c r="B34" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <v>114408026</v>
+      </c>
+      <c r="B35" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>114408201</v>
+      </c>
+      <c r="B36" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>114408501</v>
+      </c>
+      <c r="B37" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <v>114408503</v>
+      </c>
+      <c r="B38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <v>114408504</v>
+      </c>
+      <c r="B39" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <v>114408505</v>
+      </c>
+      <c r="B40" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <v>114408506</v>
+      </c>
+      <c r="B41" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A42">
+        <v>114408508</v>
+      </c>
+      <c r="B42" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A43">
+        <v>114408509</v>
+      </c>
+      <c r="B43" t="s">
+        <v>133</v>
+      </c>
+      <c r="C43" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A44">
+        <v>114408510</v>
+      </c>
+      <c r="B44" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45">
+        <v>114408511</v>
+      </c>
+      <c r="B45" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46">
+        <v>114408512</v>
+      </c>
+      <c r="B46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A47">
+        <v>114408513</v>
+      </c>
+      <c r="B47" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48">
+        <v>114408514</v>
+      </c>
+      <c r="B48" t="s">
+        <v>141</v>
+      </c>
+      <c r="C48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49">
+        <v>114408515</v>
+      </c>
+      <c r="B49" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50">
+        <v>114408516</v>
+      </c>
+      <c r="B50" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A51">
+        <v>114408517</v>
+      </c>
+      <c r="B51" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52">
+        <v>114408518</v>
+      </c>
+      <c r="B52" t="s">
+        <v>147</v>
+      </c>
+      <c r="C52" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A53">
+        <v>114408519</v>
+      </c>
+      <c r="B53" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54">
+        <v>114408520</v>
+      </c>
+      <c r="B54" t="s">
+        <v>151</v>
+      </c>
+      <c r="C54" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55">
+        <v>114408521</v>
+      </c>
+      <c r="B55" t="s">
+        <v>153</v>
+      </c>
+      <c r="C55" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A56">
+        <v>114408522</v>
+      </c>
+      <c r="B56" t="s">
+        <v>155</v>
+      </c>
+      <c r="C56" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A57">
+        <v>114408523</v>
+      </c>
+      <c r="B57" t="s">
+        <v>157</v>
+      </c>
+      <c r="C57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A58">
+        <v>114408524</v>
+      </c>
+      <c r="B58" t="s">
+        <v>159</v>
+      </c>
+      <c r="C58" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A59">
+        <v>114408526</v>
+      </c>
+      <c r="B59" t="s">
+        <v>161</v>
+      </c>
+      <c r="C59" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A60">
+        <v>114408527</v>
+      </c>
+      <c r="B60" t="s">
+        <v>163</v>
+      </c>
+      <c r="C60">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <v>114408528</v>
+      </c>
+      <c r="B61" t="s">
+        <v>164</v>
+      </c>
+      <c r="C61" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62">
+        <v>114408529</v>
+      </c>
+      <c r="B62" t="s">
+        <v>166</v>
+      </c>
+      <c r="C62" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A63">
+        <v>114408530</v>
+      </c>
+      <c r="B63" t="s">
+        <v>168</v>
+      </c>
+      <c r="C63">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A64">
+        <v>114408531</v>
+      </c>
+      <c r="B64" t="s">
+        <v>169</v>
+      </c>
+      <c r="C64" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A65">
+        <v>114408532</v>
+      </c>
+      <c r="B65" t="s">
+        <v>171</v>
+      </c>
+      <c r="C65">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A66">
+        <v>114408533</v>
+      </c>
+      <c r="B66" t="s">
+        <v>172</v>
+      </c>
+      <c r="C66" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A67">
+        <v>114408534</v>
+      </c>
+      <c r="B67" t="s">
+        <v>174</v>
+      </c>
+      <c r="C67" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A68">
+        <v>114408535</v>
+      </c>
+      <c r="B68" t="s">
+        <v>176</v>
+      </c>
+      <c r="C68" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A69">
+        <v>114408536</v>
+      </c>
+      <c r="B69" t="s">
+        <v>178</v>
+      </c>
+      <c r="C69" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A70">
+        <v>114408537</v>
+      </c>
+      <c r="B70" t="s">
+        <v>180</v>
+      </c>
+      <c r="C70" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A71">
+        <v>114408538</v>
+      </c>
+      <c r="B71" t="s">
+        <v>182</v>
+      </c>
+      <c r="C71" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A72">
+        <v>114408539</v>
+      </c>
+      <c r="B72" t="s">
+        <v>183</v>
+      </c>
+      <c r="C72" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A73">
+        <v>114408540</v>
+      </c>
+      <c r="B73" t="s">
+        <v>185</v>
+      </c>
+      <c r="C73">
         <v>123</v>
       </c>
     </row>
@@ -519,20 +2312,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.640625" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -541,7 +2334,7 @@
         <v>11772</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>186</v>
       </c>
       <c r="C2">
         <v>11772</v>
@@ -552,7 +2345,7 @@
         <v>112502533</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>187</v>
       </c>
       <c r="C3">
         <v>123</v>
@@ -563,9 +2356,570 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>188</v>
       </c>
       <c r="C4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>112102516</v>
+      </c>
+      <c r="B5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>112202008</v>
+      </c>
+      <c r="B6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>112206505</v>
+      </c>
+      <c r="B7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>112409020</v>
+      </c>
+      <c r="B8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>112409303</v>
+      </c>
+      <c r="B9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>112707008</v>
+      </c>
+      <c r="B10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>113101506</v>
+      </c>
+      <c r="B11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>113108507</v>
+      </c>
+      <c r="B12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>113401055</v>
+      </c>
+      <c r="B13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>114401518</v>
+      </c>
+      <c r="B14" t="s">
+        <v>205</v>
+      </c>
+      <c r="C14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>114409001</v>
+      </c>
+      <c r="B15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C15">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>114409003</v>
+      </c>
+      <c r="B16" t="s">
+        <v>208</v>
+      </c>
+      <c r="C16" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>114409004</v>
+      </c>
+      <c r="B17" t="s">
+        <v>210</v>
+      </c>
+      <c r="C17" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>114409005</v>
+      </c>
+      <c r="B18" t="s">
+        <v>212</v>
+      </c>
+      <c r="C18" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>114409006</v>
+      </c>
+      <c r="B19" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>114409007</v>
+      </c>
+      <c r="B20" t="s">
+        <v>215</v>
+      </c>
+      <c r="C20">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>114409008</v>
+      </c>
+      <c r="B21" t="s">
+        <v>216</v>
+      </c>
+      <c r="C21">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>114409012</v>
+      </c>
+      <c r="B22" t="s">
+        <v>217</v>
+      </c>
+      <c r="C22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>114409014</v>
+      </c>
+      <c r="B23" t="s">
+        <v>218</v>
+      </c>
+      <c r="C23" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>114409015</v>
+      </c>
+      <c r="B24" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>114409016</v>
+      </c>
+      <c r="B25" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>114409018</v>
+      </c>
+      <c r="B26" t="s">
+        <v>223</v>
+      </c>
+      <c r="C26">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>114409019</v>
+      </c>
+      <c r="B27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C27">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <v>114409022</v>
+      </c>
+      <c r="B28" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <v>114409201</v>
+      </c>
+      <c r="B29" t="s">
+        <v>227</v>
+      </c>
+      <c r="C29" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>114409501</v>
+      </c>
+      <c r="B30" t="s">
+        <v>229</v>
+      </c>
+      <c r="C30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <v>114409504</v>
+      </c>
+      <c r="B31" t="s">
+        <v>231</v>
+      </c>
+      <c r="C31" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>114409506</v>
+      </c>
+      <c r="B32" t="s">
+        <v>233</v>
+      </c>
+      <c r="C32" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>114409507</v>
+      </c>
+      <c r="B33" t="s">
+        <v>235</v>
+      </c>
+      <c r="C33" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>114409508</v>
+      </c>
+      <c r="B34" t="s">
+        <v>237</v>
+      </c>
+      <c r="C34" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <v>114409509</v>
+      </c>
+      <c r="B35" t="s">
+        <v>239</v>
+      </c>
+      <c r="C35" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>114409511</v>
+      </c>
+      <c r="B36" t="s">
+        <v>241</v>
+      </c>
+      <c r="C36">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>114409513</v>
+      </c>
+      <c r="B37" t="s">
+        <v>242</v>
+      </c>
+      <c r="C37" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <v>114409516</v>
+      </c>
+      <c r="B38" t="s">
+        <v>244</v>
+      </c>
+      <c r="C38">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <v>114409518</v>
+      </c>
+      <c r="B39" t="s">
+        <v>245</v>
+      </c>
+      <c r="C39" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <v>114409519</v>
+      </c>
+      <c r="B40" t="s">
+        <v>247</v>
+      </c>
+      <c r="C40">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <v>114409520</v>
+      </c>
+      <c r="B41" t="s">
+        <v>248</v>
+      </c>
+      <c r="C41" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A42">
+        <v>114409521</v>
+      </c>
+      <c r="B42" t="s">
+        <v>250</v>
+      </c>
+      <c r="C42" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A43">
+        <v>114409522</v>
+      </c>
+      <c r="B43" t="s">
+        <v>252</v>
+      </c>
+      <c r="C43" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A44">
+        <v>114409525</v>
+      </c>
+      <c r="B44" t="s">
+        <v>254</v>
+      </c>
+      <c r="C44">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45">
+        <v>114409526</v>
+      </c>
+      <c r="B45" t="s">
+        <v>255</v>
+      </c>
+      <c r="C45" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46">
+        <v>114409528</v>
+      </c>
+      <c r="B46" t="s">
+        <v>257</v>
+      </c>
+      <c r="C46" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A47">
+        <v>114409533</v>
+      </c>
+      <c r="B47" t="s">
+        <v>259</v>
+      </c>
+      <c r="C47">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48">
+        <v>114409534</v>
+      </c>
+      <c r="B48" t="s">
+        <v>260</v>
+      </c>
+      <c r="C48">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49">
+        <v>114409535</v>
+      </c>
+      <c r="B49" t="s">
+        <v>261</v>
+      </c>
+      <c r="C49" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50">
+        <v>114409536</v>
+      </c>
+      <c r="B50" t="s">
+        <v>263</v>
+      </c>
+      <c r="C50" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A51">
+        <v>114409537</v>
+      </c>
+      <c r="B51" t="s">
+        <v>265</v>
+      </c>
+      <c r="C51">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52">
+        <v>114409538</v>
+      </c>
+      <c r="B52" t="s">
+        <v>266</v>
+      </c>
+      <c r="C52" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A53">
+        <v>114409601</v>
+      </c>
+      <c r="B53" t="s">
+        <v>268</v>
+      </c>
+      <c r="C53" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54">
+        <v>114409602</v>
+      </c>
+      <c r="B54" t="s">
+        <v>270</v>
+      </c>
+      <c r="C54">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55">
+        <v>114421601</v>
+      </c>
+      <c r="B55" t="s">
+        <v>271</v>
+      </c>
+      <c r="C55">
         <v>123</v>
       </c>
     </row>
@@ -577,29 +2931,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" s="2">
+      <c r="A2">
         <v>11247156</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
       <c r="C2">
         <v>123</v>
@@ -610,125 +2961,385 @@
         <v>11344114</v>
       </c>
       <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>3119495</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>11150227</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>11240297</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>11240300</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>11240316</v>
+      </c>
+      <c r="B9" t="s">
         <v>11</v>
       </c>
-      <c r="C3">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="2">
-        <v>103</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
+      <c r="A10">
+        <v>11340171</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <v>123</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
+      <c r="A11">
+        <v>11340209</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
+      <c r="A12">
+        <v>11340215</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
+      <c r="A13">
+        <v>11340217</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="A14">
+        <v>11340222</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14">
+        <v>123</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+      <c r="A15">
+        <v>11340234</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B30" s="2"/>
+      <c r="A16">
+        <v>11340241</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>11340244</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>11340245</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>11440176</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>11440187</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>11440189</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>11440191</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>11440195</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>11440198</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>11440210</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>11440216</v>
+      </c>
+      <c r="B26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>11440223</v>
+      </c>
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <v>11440229</v>
+      </c>
+      <c r="B28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <v>11440235</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>11440245</v>
+      </c>
+      <c r="B30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <v>11440246</v>
+      </c>
+      <c r="B31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>11440270</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>11440272</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>11440273</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <v>11440274</v>
+      </c>
+      <c r="B35" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>11440275</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>11440276</v>
+      </c>
+      <c r="B37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37">
+        <v>123</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -737,18 +3348,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2A4A90-8B70-4C51-B786-7CA387C25B38}">
-  <dimension ref="A1:C2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -757,20 +3368,746 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="C2">
         <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>4112234</v>
+      </c>
+      <c r="B3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>11139137</v>
+      </c>
+      <c r="B4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>11241118</v>
+      </c>
+      <c r="B5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>11241121</v>
+      </c>
+      <c r="B6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>11241128</v>
+      </c>
+      <c r="B7" t="s">
+        <v>278</v>
+      </c>
+      <c r="C7">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>11241144</v>
+      </c>
+      <c r="B8" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>11241362</v>
+      </c>
+      <c r="B9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>11241406</v>
+      </c>
+      <c r="B10" t="s">
+        <v>282</v>
+      </c>
+      <c r="C10">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>11341113</v>
+      </c>
+      <c r="B11" t="s">
+        <v>283</v>
+      </c>
+      <c r="C11">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>11341123</v>
+      </c>
+      <c r="B12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C12">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>11341125</v>
+      </c>
+      <c r="B13" t="s">
+        <v>285</v>
+      </c>
+      <c r="C13">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>11341128</v>
+      </c>
+      <c r="B14" t="s">
+        <v>286</v>
+      </c>
+      <c r="C14" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>11341143</v>
+      </c>
+      <c r="B15" t="s">
+        <v>288</v>
+      </c>
+      <c r="C15" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>11341146</v>
+      </c>
+      <c r="B16" t="s">
+        <v>290</v>
+      </c>
+      <c r="C16" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>11341152</v>
+      </c>
+      <c r="B17" t="s">
+        <v>292</v>
+      </c>
+      <c r="C17">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>11343339</v>
+      </c>
+      <c r="B18" t="s">
+        <v>293</v>
+      </c>
+      <c r="C18" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>11441101</v>
+      </c>
+      <c r="B19" t="s">
+        <v>295</v>
+      </c>
+      <c r="C19">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>11441102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>11441103</v>
+      </c>
+      <c r="B21" t="s">
+        <v>297</v>
+      </c>
+      <c r="C21">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>11441104</v>
+      </c>
+      <c r="B22" t="s">
+        <v>298</v>
+      </c>
+      <c r="C22">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>11441105</v>
+      </c>
+      <c r="B23" t="s">
+        <v>299</v>
+      </c>
+      <c r="C23">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>11441106</v>
+      </c>
+      <c r="B24" t="s">
+        <v>300</v>
+      </c>
+      <c r="C24">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>11441107</v>
+      </c>
+      <c r="B25" t="s">
+        <v>301</v>
+      </c>
+      <c r="C25" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>11441108</v>
+      </c>
+      <c r="B26" t="s">
+        <v>303</v>
+      </c>
+      <c r="C26">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>11441109</v>
+      </c>
+      <c r="B27" t="s">
+        <v>304</v>
+      </c>
+      <c r="C27">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <v>11441110</v>
+      </c>
+      <c r="B28" t="s">
+        <v>305</v>
+      </c>
+      <c r="C28">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <v>11441111</v>
+      </c>
+      <c r="B29" t="s">
+        <v>306</v>
+      </c>
+      <c r="C29">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>11441112</v>
+      </c>
+      <c r="B30" t="s">
+        <v>307</v>
+      </c>
+      <c r="C30">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <v>11441115</v>
+      </c>
+      <c r="B31" t="s">
+        <v>308</v>
+      </c>
+      <c r="C31">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>11441116</v>
+      </c>
+      <c r="B32" t="s">
+        <v>309</v>
+      </c>
+      <c r="C32" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>11441117</v>
+      </c>
+      <c r="B33" t="s">
+        <v>311</v>
+      </c>
+      <c r="C33" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>11441118</v>
+      </c>
+      <c r="B34" t="s">
+        <v>313</v>
+      </c>
+      <c r="C34" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <v>11441119</v>
+      </c>
+      <c r="B35" t="s">
+        <v>315</v>
+      </c>
+      <c r="C35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>11441120</v>
+      </c>
+      <c r="B36" t="s">
+        <v>316</v>
+      </c>
+      <c r="C36">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>11441121</v>
+      </c>
+      <c r="B37" t="s">
+        <v>317</v>
+      </c>
+      <c r="C37">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <v>11441122</v>
+      </c>
+      <c r="B38" t="s">
+        <v>318</v>
+      </c>
+      <c r="C38">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <v>11441123</v>
+      </c>
+      <c r="B39" t="s">
+        <v>319</v>
+      </c>
+      <c r="C39">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <v>11441124</v>
+      </c>
+      <c r="B40" t="s">
+        <v>320</v>
+      </c>
+      <c r="C40">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <v>11441125</v>
+      </c>
+      <c r="B41" t="s">
+        <v>321</v>
+      </c>
+      <c r="C41">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A42">
+        <v>11441126</v>
+      </c>
+      <c r="B42" t="s">
+        <v>322</v>
+      </c>
+      <c r="C42" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A43">
+        <v>11441127</v>
+      </c>
+      <c r="B43" t="s">
+        <v>324</v>
+      </c>
+      <c r="C43">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A44">
+        <v>11441128</v>
+      </c>
+      <c r="B44" t="s">
+        <v>325</v>
+      </c>
+      <c r="C44">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45">
+        <v>11441130</v>
+      </c>
+      <c r="B45" t="s">
+        <v>326</v>
+      </c>
+      <c r="C45">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46">
+        <v>11441131</v>
+      </c>
+      <c r="B46" t="s">
+        <v>327</v>
+      </c>
+      <c r="C46">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A47">
+        <v>11441132</v>
+      </c>
+      <c r="B47" t="s">
+        <v>328</v>
+      </c>
+      <c r="C47">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48">
+        <v>11441133</v>
+      </c>
+      <c r="B48" t="s">
+        <v>329</v>
+      </c>
+      <c r="C48">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49">
+        <v>11441134</v>
+      </c>
+      <c r="B49" t="s">
+        <v>330</v>
+      </c>
+      <c r="C49" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50">
+        <v>11441135</v>
+      </c>
+      <c r="B50" t="s">
+        <v>332</v>
+      </c>
+      <c r="C50">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A51">
+        <v>11441136</v>
+      </c>
+      <c r="B51" t="s">
+        <v>333</v>
+      </c>
+      <c r="C51">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52">
+        <v>11441137</v>
+      </c>
+      <c r="B52" t="s">
+        <v>334</v>
+      </c>
+      <c r="C52">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A53">
+        <v>11441138</v>
+      </c>
+      <c r="B53" t="s">
+        <v>335</v>
+      </c>
+      <c r="C53">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54">
+        <v>11441139</v>
+      </c>
+      <c r="B54" t="s">
+        <v>336</v>
+      </c>
+      <c r="C54">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55">
+        <v>11441140</v>
+      </c>
+      <c r="B55" t="s">
+        <v>337</v>
+      </c>
+      <c r="C55">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A56">
+        <v>11441142</v>
+      </c>
+      <c r="B56" t="s">
+        <v>338</v>
+      </c>
+      <c r="C56">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A57">
+        <v>11441143</v>
+      </c>
+      <c r="B57" t="s">
+        <v>339</v>
+      </c>
+      <c r="C57" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A58">
+        <v>11441145</v>
+      </c>
+      <c r="B58" t="s">
+        <v>341</v>
+      </c>
+      <c r="C58">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A59">
+        <v>11441146</v>
+      </c>
+      <c r="B59" t="s">
+        <v>342</v>
+      </c>
+      <c r="C59">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A60">
+        <v>11441147</v>
+      </c>
+      <c r="B60" t="s">
+        <v>343</v>
+      </c>
+      <c r="C60">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <v>11441150</v>
+      </c>
+      <c r="B61" t="s">
+        <v>344</v>
+      </c>
+      <c r="C61">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62">
+        <v>11441151</v>
+      </c>
+      <c r="B62" t="s">
+        <v>345</v>
+      </c>
+      <c r="C62" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A63">
+        <v>11441152</v>
+      </c>
+      <c r="B63" t="s">
+        <v>347</v>
+      </c>
+      <c r="C63">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A64">
+        <v>11441153</v>
+      </c>
+      <c r="B64" t="s">
+        <v>348</v>
+      </c>
+      <c r="C64">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A65">
+        <v>11441154</v>
+      </c>
+      <c r="B65" t="s">
+        <v>349</v>
+      </c>
+      <c r="C65">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A66">
+        <v>11441155</v>
+      </c>
+      <c r="B66" t="s">
+        <v>350</v>
+      </c>
+      <c r="C66" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A67">
+        <v>11441170</v>
+      </c>
+      <c r="B67" t="s">
+        <v>352</v>
+      </c>
+      <c r="C67" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A68">
+        <v>11441171</v>
+      </c>
+      <c r="B68" t="s">
+        <v>354</v>
+      </c>
+      <c r="C68" t="s">
+        <v>355</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <sheetData>
